--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Acumulado_desde_2018" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$97</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,8 +535,16 @@
         <v>10.81</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1514,8 +1522,184 @@
         <v>15.53</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>-37.23</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>-55.93</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>-18.92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>40.34</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>32.72</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>48.57</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>50.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>-42.31</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>60.08</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>-29.53</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>26.54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C81"/>
+  <autoFilter ref="A1:C97"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
